--- a/Data/Results/System/phase_segmentation_revised_log.xlsx
+++ b/Data/Results/System/phase_segmentation_revised_log.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,151 +425,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pair_workbook</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>route_category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>applied_stop_threshold_seconds</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ev_manual_match</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ice_manual_match</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ev_manual_stop_events</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ev_manual_stop_matches</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ev_manual_stop_start_inferred_events</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ev_manual_stop_start_inferred_rows</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ice_manual_stop_events</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ice_manual_stop_matches</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ice_manual_stop_start_inferred_events</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ice_manual_stop_start_inferred_rows</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ev_manual_replenishment_rows</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>ice_manual_replenishment_rows</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ev_charging_stop_conflicts_resolved</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ice_charging_stop_conflicts_resolved</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ev_final_charging_time_min</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ice_final_refueling_time_min</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ev_rule_gap_rows</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ice_rule_gap_rows</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ev_recorded_zero_speed_episodes</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ice_recorded_zero_speed_episodes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ev_recorded_zero_speed_stop_rows</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ice_recorded_zero_speed_stop_rows</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>ev_recorded_zero_speed_idle_rows</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ice_recorded_zero_speed_idle_rows</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -566,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_001_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_002_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,12 +591,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -600,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -627,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -636,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -648,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -663,7 +675,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_002_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_001_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -676,12 +688,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -724,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -733,19 +745,19 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -760,7 +772,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_003_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -773,12 +785,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -794,19 +806,19 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -818,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>22.91666666666667</v>
+        <v>21.51666666666667</v>
       </c>
       <c r="S4" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -830,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -857,7 +869,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_004_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_003_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -870,12 +882,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -918,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -954,7 +966,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -967,16 +979,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1024,19 +1036,19 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1051,7 +1063,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_006_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1064,16 +1076,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1085,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1112,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1121,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1148,7 +1160,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_007_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1161,16 +1173,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1209,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1245,7 +1257,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_008_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1258,16 +1270,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1279,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1306,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1342,7 +1354,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_009_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1355,16 +1367,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1403,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1415,13 +1427,13 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1439,7 +1451,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_010_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1452,37 +1464,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1500,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1536,7 +1548,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_011_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1549,25 +1561,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1594,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1633,7 +1645,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_012_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1646,37 +1658,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1691,10 +1703,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1730,7 +1742,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_013_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1743,37 +1755,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1791,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1827,7 +1839,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_014_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1840,37 +1852,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1888,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1924,7 +1936,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1937,37 +1949,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1985,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1994,19 +2006,19 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2021,7 +2033,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2034,37 +2046,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2082,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -2118,7 +2130,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_017_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2131,37 +2143,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2179,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -2215,7 +2227,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_018_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2228,37 +2240,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NOT MATCHED</t>
+          <t>MATCHED</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2276,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2308,6 +2320,1946 @@
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>180</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>180</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16</v>
+      </c>
+      <c r="K21" t="n">
+        <v>15</v>
+      </c>
+      <c r="L21" t="n">
+        <v>15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>15</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>180</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>29</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>29</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>180</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>14</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>180</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>14</v>
+      </c>
+      <c r="G24" t="n">
+        <v>13</v>
+      </c>
+      <c r="H24" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>180</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>180</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>180</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" t="n">
+        <v>7</v>
+      </c>
+      <c r="L27" t="n">
+        <v>7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>7</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>180</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>13</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>180</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7</v>
+      </c>
+      <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>180</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>29</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>180</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>180</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" t="n">
+        <v>18</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" t="n">
+        <v>18</v>
+      </c>
+      <c r="J32" t="n">
+        <v>9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M32" t="n">
+        <v>9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>8</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>180</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>7</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>6</v>
+      </c>
+      <c r="M33" t="n">
+        <v>6</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>180</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.383333333333333</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>180</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>180</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>180</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>180</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>21.51666666666667</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>180</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/Results/System/phase_segmentation_revised_log.xlsx
+++ b/Data/Results/System/phase_segmentation_revised_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PAIR_002_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_053_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -612,20 +612,20 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>44.68333333333333</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -648,19 +648,19 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
+        <v>4</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2</v>
       </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -675,7 +675,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PAIR_001_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_054_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -745,22 +745,22 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X3" t="n">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z3" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_002_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -818,7 +818,7 @@
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>263</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>21.51666666666667</v>
+        <v>30</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -842,19 +842,19 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>255</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -869,7 +869,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PAIR_003_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+          <t>PAIR_001_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -939,19 +939,19 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+          <t>PAIR_037_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -988,31 +988,31 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1036,19 +1036,19 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+          <t>PAIR_003_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1085,32 +1085,32 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>38.33333333333334</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_038_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1230,19 +1230,19 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_040_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1279,67 +1279,67 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_041_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>44.68333333333333</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1424,19 +1424,19 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_039_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1473,70 +1473,70 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>50.36666666666667</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z11" t="n">
         <v>8</v>
       </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_042_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1570,67 +1570,67 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>8</v>
       </c>
-      <c r="G12" t="n">
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z12" t="n">
         <v>6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_045_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1667,70 +1667,70 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z13" t="n">
         <v>10</v>
       </c>
-      <c r="L13" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_046_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1764,67 +1764,67 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z14" t="n">
         <v>8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>9</v>
-      </c>
-      <c r="M14" t="n">
-        <v>9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_043_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1861,67 +1861,67 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z15" t="n">
         <v>10</v>
-      </c>
-      <c r="L15" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_044_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1958,28 +1958,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2006,19 +2006,19 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2055,28 +2055,28 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
         <v>11</v>
       </c>
-      <c r="G17" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" t="n">
-        <v>9</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>16</v>
-      </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2227,7 +2227,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2249,28 +2249,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2346,28 +2346,28 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
         <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2446,25 +2446,25 @@
         <v>7</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2543,25 +2543,25 @@
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2588,16 +2588,16 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_010_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2637,28 +2637,28 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -2685,19 +2685,19 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2712,7 +2712,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_011_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2734,28 +2734,28 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2809,7 +2809,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2831,28 +2831,28 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2928,28 +2928,28 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16</v>
+      </c>
+      <c r="K26" t="n">
         <v>15</v>
       </c>
-      <c r="H26" t="n">
-        <v>7</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="L26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2976,19 +2976,19 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3100,7 +3100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3122,28 +3122,28 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3219,28 +3219,28 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3270,13 +3270,13 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -3294,7 +3294,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_017_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3319,25 +3319,25 @@
         <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I30" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_018_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3413,28 +3413,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3510,16 +3510,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G32" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J32" t="n">
         <v>9</v>
@@ -3558,19 +3558,19 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_020_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3610,25 +3610,25 @@
         <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -3682,7 +3682,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_021_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3704,31 +3704,31 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.383333333333333</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3755,13 +3755,13 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_022_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3801,28 +3801,28 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -3849,19 +3849,19 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_023_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3898,28 +3898,28 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_024_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3995,28 +3995,28 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4043,13 +4043,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>PAIR_025_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4092,31 +4092,31 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>21.51666666666667</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -4140,13 +4140,13 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+          <t>PAIR_026_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4189,28 +4189,28 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4240,13 +4240,13 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -4260,6 +4260,1558 @@
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PAIR_027_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>180</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" t="n">
+        <v>31</v>
+      </c>
+      <c r="H40" t="n">
+        <v>8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>31</v>
+      </c>
+      <c r="J40" t="n">
+        <v>9</v>
+      </c>
+      <c r="K40" t="n">
+        <v>9</v>
+      </c>
+      <c r="L40" t="n">
+        <v>9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>9</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PAIR_047_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>180</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4</v>
+      </c>
+      <c r="W41" t="n">
+        <v>5</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PAIR_028_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>180</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" t="n">
+        <v>9</v>
+      </c>
+      <c r="K42" t="n">
+        <v>9</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9</v>
+      </c>
+      <c r="M42" t="n">
+        <v>9</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PAIR_029_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>180</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" t="n">
+        <v>11</v>
+      </c>
+      <c r="K43" t="n">
+        <v>12</v>
+      </c>
+      <c r="L43" t="n">
+        <v>10</v>
+      </c>
+      <c r="M43" t="n">
+        <v>12</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>5</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PAIR_030_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>180</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10</v>
+      </c>
+      <c r="G44" t="n">
+        <v>18</v>
+      </c>
+      <c r="H44" t="n">
+        <v>10</v>
+      </c>
+      <c r="I44" t="n">
+        <v>18</v>
+      </c>
+      <c r="J44" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" t="n">
+        <v>9</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9</v>
+      </c>
+      <c r="M44" t="n">
+        <v>9</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>8</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PAIR_031_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>180</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6</v>
+      </c>
+      <c r="M45" t="n">
+        <v>6</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PAIR_033_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>180</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>4</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PAIR_034_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>180</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>7</v>
+      </c>
+      <c r="I47" t="n">
+        <v>7</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PAIR_035_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>180</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>9</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6</v>
+      </c>
+      <c r="L48" t="n">
+        <v>6</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PAIR_032_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>180</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PAIR_048_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>180</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>5</v>
+      </c>
+      <c r="W50" t="n">
+        <v>2</v>
+      </c>
+      <c r="X50" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PAIR_049_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>180</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>5</v>
+      </c>
+      <c r="X51" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PAIR_050_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>180</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>10</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>5</v>
+      </c>
+      <c r="W52" t="n">
+        <v>2</v>
+      </c>
+      <c r="X52" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PAIR_051_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>180</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" t="n">
+        <v>15</v>
+      </c>
+      <c r="H53" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" t="n">
+        <v>11</v>
+      </c>
+      <c r="K53" t="n">
+        <v>18</v>
+      </c>
+      <c r="L53" t="n">
+        <v>11</v>
+      </c>
+      <c r="M53" t="n">
+        <v>18</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>8</v>
+      </c>
+      <c r="W53" t="n">
+        <v>5</v>
+      </c>
+      <c r="X53" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PAIR_052_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>180</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" t="n">
+        <v>31</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8</v>
+      </c>
+      <c r="I54" t="n">
+        <v>31</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" t="n">
+        <v>5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>5</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>3</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PAIR_036_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>INTERCITY</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>180</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MATCHED</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>5</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
